--- a/03_test-cases/v1.0/fragments/TC-DANGTIN-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-DANGTIN-v1.0.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$6:$U$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -462,7 +462,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -677,6 +677,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
         <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -914,7 +924,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="256">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1655,6 +1665,8 @@
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5072,7 +5084,7 @@
       </c>
       <c r="C34" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D34" s="229" t="inlineStr">
@@ -5796,7 +5808,7 @@
       </c>
       <c r="C41" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D41" s="229" t="inlineStr">
@@ -5900,7 +5912,7 @@
       </c>
       <c r="C42" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D42" s="229" t="inlineStr">
@@ -6002,7 +6014,7 @@
       </c>
       <c r="C43" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D43" s="229" t="inlineStr">
@@ -9108,7 +9120,7 @@
       </c>
       <c r="C73" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D73" s="229" t="inlineStr">
@@ -9211,7 +9223,7 @@
       </c>
       <c r="C74" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D74" s="229" t="inlineStr">
@@ -9314,7 +9326,7 @@
       </c>
       <c r="C75" s="229" t="inlineStr">
         <is>
-          <t>BA xác nhận qua trao đổi (chat), 2026-07-29</t>
+          <t>BA xác nhận qua chat (2026-07-29)</t>
         </is>
       </c>
       <c r="D75" s="229" t="inlineStr">
@@ -11544,7 +11556,7 @@
       </c>
       <c r="AP97" s="205" t="inlineStr">
         <is>
-          <t>Technique: VAL-02-inline-blur</t>
+          <t>Technique: N/A — baseline (derive trực tiếp từ rule VAL-02, BRD v3.2 §D8.3; không thuộc rubric B1–B8) | Sửa 2026-07-30 theo finding review-tc m5 (R1-17): trước đây tag sai thành "VAL-02-…" trong khi VAL-02 là rule ID của BRD v3.2 §D8.3, không phải test design technique</t>
         </is>
       </c>
       <c r="AQ97" s="205" t="n"/>
@@ -11649,7 +11661,7 @@
       </c>
       <c r="AP98" s="205" t="inlineStr">
         <is>
-          <t>Technique: VAL-02-scroll-to-first-error</t>
+          <t>Technique: N/A — baseline (derive trực tiếp từ rule VAL-02, BRD v3.2 §D8.3; không thuộc rubric B1–B8) | Sửa 2026-07-30 theo finding review-tc m5 (R1-17)</t>
         </is>
       </c>
       <c r="AQ98" s="205" t="n"/>
@@ -13008,10 +13020,10 @@
       </c>
       <c r="I115" s="245" t="inlineStr">
         <is>
-          <t>1. Field hiển thị đúng giá trị mặc định
-2. Field nhận đúng giá trị vừa nhập
-3. Field hiển thị đúng giá trị mặc định
-4. Checkbox chuyển sang trạng thái đã tick
+          <t>1. Field Điểm xuất phát hiển thị đúng giá trị mặc định 'Tòa nhà Lô B3, KCX Tân Thuận, Q.7'
+2. Field Điểm đến nhận đúng giá trị vừa nhập '89 Nguyễn Thị Minh Khai, Q.3'
+3. Field Thời gian di chuyển hiển thị đúng giá trị mặc định 17:30–18:30 (BRD v3.2 §D8.2)
+4. Checkbox điều khoản chuyển sang trạng thái đã tick
 5. Tuyến được ghi nhận thành công, KHÔNG công khai lên bảng tin, chờ hệ thống tự động khớp với tin NEED phù hợp</t>
         </is>
       </c>
@@ -13068,7 +13080,11 @@
         <f>IFERROR(IF($AJ115&lt;&gt;"",$AJ115,IF($AE115&lt;&gt;"",$AE115,IF($Z115&lt;&gt;"",$Z115,IF($U115&lt;&gt;"",$U115,IF($P115&lt;&gt;"",$P115,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP115" s="205" t="n"/>
+      <c r="AP115" s="205" t="inlineStr">
+        <is>
+          <t>Sửa 2026-07-30 theo finding review-tc m6 (R3-12): Expected bước 1 và 3 trước đây ghi "Field hiển thị đúng giá trị mặc định" mà không nêu giá trị → nay ghi thẳng giá trị, khớp BRD v3.2 §D8.2 + test_data_catalog.md</t>
+        </is>
+      </c>
       <c r="AQ115" s="205" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="206">
@@ -14482,7 +14498,7 @@
       </c>
       <c r="I130" s="245" t="inlineStr">
         <is>
-          <t>1. Màn hiển thị đúng thông tin tin
+          <t>1. Màn hiển thị đúng tin đang mở: tên tin + badge trạng thái 'Đã ghép'
 2. KHÔNG còn nút 'Chỉnh sửa' hiển thị (khoá hoàn toàn)</t>
         </is>
       </c>
@@ -14541,7 +14557,7 @@
       </c>
       <c r="AP130" s="205" t="inlineStr">
         <is>
-          <t>Technique: ST-invalid-edit-MATCHED</t>
+          <t>Technique: ST-invalid-edit-MATCHED | Sửa 2026-07-30 theo finding review-tc m7 (R3-12): Expected bước 1 trước đây là "Màn hiển thị đúng thông tin tin" (mơ hồ) → nay nêu rõ tên tin + badge 'Đã ghép'</t>
         </is>
       </c>
       <c r="AQ130" s="205" t="n"/>
@@ -25358,7 +25374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="206" min="1" max="1"/>
@@ -25764,7 +25780,7 @@
       </c>
       <c r="M6" s="249" t="inlineStr">
         <is>
-          <t>100% (1/1)</t>
+          <t>0 TC tại module này — cover tại TC_01 Hoạt động (TC_01.9/TC_01.10), xem sheet Coverage Matrix</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26564,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="206">
       <c r="A19" s="250" t="inlineStr">
         <is>
           <t>SC-ORD-030</t>
@@ -26613,64 +26629,194 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="252" t="inlineStr">
-        <is>
-          <t>Total scenarios: 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="252" t="inlineStr">
-        <is>
-          <t>Total TCs derived: 100</t>
+    <row r="20" s="206">
+      <c r="A20" s="250" t="inlineStr">
+        <is>
+          <t>SC-ORD-031</t>
+        </is>
+      </c>
+      <c r="B20" s="251" t="inlineStr">
+        <is>
+          <t>Địa chỉ lấy hàng (Người gửi) — autocomplete + editability (Tên read-only, SĐT bắt buộc/validate)</t>
+        </is>
+      </c>
+      <c r="C20" s="251" t="inlineStr">
+        <is>
+          <t>Gõ text hiện gợi ý, PHẢI chọn từ danh sách (không lưu tự do), không phân biệt hoa/thường…</t>
+        </is>
+      </c>
+      <c r="D20" s="254" t="inlineStr">
+        <is>
+          <t>✅ 4 (EP-suggest-selected; EP-suggest-not-selected → không lưu; EP-sdt-valid; EP-sdt-invalid)</t>
+        </is>
+      </c>
+      <c r="E20" s="255" t="inlineStr">
+        <is>
+          <t>N/A: no range field</t>
+        </is>
+      </c>
+      <c r="F20" s="255" t="inlineStr">
+        <is>
+          <t>N/A: single condition (chọn/không chọn gợi ý)</t>
+        </is>
+      </c>
+      <c r="G20" s="255" t="inlineStr">
+        <is>
+          <t>N/A: no lifecycle</t>
+        </is>
+      </c>
+      <c r="H20" s="255" t="inlineStr">
+        <is>
+          <t>N/A: &lt;3 params</t>
+        </is>
+      </c>
+      <c r="I20" s="254" t="inlineStr">
+        <is>
+          <t>✅ 3 (EG-case-insensitive; EG-empty-sdt; EG-readonly-Tên)</t>
+        </is>
+      </c>
+      <c r="J20" s="255" t="inlineStr">
+        <is>
+          <t>N/A: not CRUD</t>
+        </is>
+      </c>
+      <c r="K20" s="255" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="250" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" s="249" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="206">
+      <c r="A21" s="250" t="inlineStr">
+        <is>
+          <t>SC-ORD-032</t>
+        </is>
+      </c>
+      <c r="B21" s="251" t="inlineStr">
+        <is>
+          <t>Địa chỉ giao hàng (Người nhận) — autocomplete + SĐT bắt buộc/validate</t>
+        </is>
+      </c>
+      <c r="C21" s="251" t="inlineStr">
+        <is>
+          <t>Gõ text hiện gợi ý, PHẢI chọn từ danh sách (không lưu tự do), không phân biệt hoa/thường…</t>
+        </is>
+      </c>
+      <c r="D21" s="254" t="inlineStr">
+        <is>
+          <t>✅ 4 (EP-suggest-selected; EP-suggest-not-selected → không lưu; EP-sdt-valid; EP-sdt-invalid)</t>
+        </is>
+      </c>
+      <c r="E21" s="255" t="inlineStr">
+        <is>
+          <t>N/A: no range field</t>
+        </is>
+      </c>
+      <c r="F21" s="255" t="inlineStr">
+        <is>
+          <t>N/A: single condition (chọn/không chọn gợi ý)</t>
+        </is>
+      </c>
+      <c r="G21" s="255" t="inlineStr">
+        <is>
+          <t>N/A: no lifecycle</t>
+        </is>
+      </c>
+      <c r="H21" s="255" t="inlineStr">
+        <is>
+          <t>N/A: &lt;3 params</t>
+        </is>
+      </c>
+      <c r="I21" s="254" t="inlineStr">
+        <is>
+          <t>✅ 2 (EG-case-insensitive; EG-empty-sdt)</t>
+        </is>
+      </c>
+      <c r="J21" s="255" t="inlineStr">
+        <is>
+          <t>N/A: not CRUD</t>
+        </is>
+      </c>
+      <c r="K21" s="255" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="250" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" s="249" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="252" t="inlineStr">
         <is>
-          <t>Average coverage %: 100% (mọi technique applicable đều đã apply; 5 SC 0-dim/completeness-only đã log lý do — SC-002/004/006/010/011)</t>
+          <t>Total scenarios: 20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="252" t="inlineStr">
         <is>
-          <t>Most-applied technique: B2 BVA (23 TCs: SC-027=18, SC-028=5)</t>
+          <t>Total TCs derived: 109</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="252" t="inlineStr">
         <is>
+          <t>Average coverage %: 100% (mọi technique applicable đều đã apply; 5 SC 0-dim/completeness-only đã log lý do — SC-002/004/006/010/011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="252" t="inlineStr">
+        <is>
+          <t>Most-applied technique: B2 BVA (23 TCs: SC-027=18, SC-028=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="252" t="inlineStr">
+        <is>
           <t>Least-applied technique (áp dụng, khác N/A): B3 DT (4 TCs: SC-030)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="253" t="inlineStr">
-        <is>
-          <t>B5 PW: N/A toàn module — không scenario nào có ≥3 tham số nhân (multiplicative params) trong phạm vi Đăng tin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="253" t="inlineStr">
-        <is>
-          <t>B7 CRUD: N/A toàn module — CRUD ops chia theo module khác (Delete→CNL 'Huỷ đơn', List→TC-HOATDONG fragment); Create/Update trong phạm vi này đã có TC baseline riêng (SC-001/002/008), không tách thêm CRUD matrix trùng lặp.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="253" t="inlineStr">
         <is>
+          <t>B5 PW: N/A toàn module — không scenario nào có ≥3 tham số nhân (multiplicative params) trong phạm vi Đăng tin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="253" t="inlineStr">
+        <is>
+          <t>B7 CRUD: N/A toàn module — CRUD ops chia theo module khác (Delete→CNL 'Huỷ đơn', List→TC-HOATDONG fragment); Create/Update trong phạm vi này đã có TC baseline riêng (SC-001/002/008), không tách thêm CRUD matrix trùng lặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="253" t="inlineStr">
+        <is>
           <t>B8 CEG: N/A toàn module — B3 DT (SC-030) chỉ 3 rules sau collapse, không vượt ngưỡng 16 rules cần escalate.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/03_test-cases/v1.0/fragments/TC-DANGTIN-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-DANGTIN-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Đăng tin" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
